--- a/tests/fixtures/calce/CS2_TEST/CS2_TEST_session2.xlsx
+++ b/tests/fixtures/calce/CS2_TEST/CS2_TEST_session2.xlsx
@@ -773,10 +773,10 @@
         <v>4.2</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>1.0908</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="I12" t="n">
         <v>25.2</v>
@@ -802,10 +802,10 @@
         <v>4.140000000000001</v>
       </c>
       <c r="G13" t="n">
-        <v>0.1200777777777778</v>
+        <v>1.210877777777778</v>
       </c>
       <c r="H13" t="n">
-        <v>0.1188888888888889</v>
+        <v>1.198888888888889</v>
       </c>
       <c r="I13" t="n">
         <v>25.2</v>
@@ -831,10 +831,10 @@
         <v>4.08</v>
       </c>
       <c r="G14" t="n">
-        <v>0.2401555555555556</v>
+        <v>1.330955555555556</v>
       </c>
       <c r="H14" t="n">
-        <v>0.2377777777777778</v>
+        <v>1.317777777777778</v>
       </c>
       <c r="I14" t="n">
         <v>25.2</v>
@@ -860,10 +860,10 @@
         <v>4.02</v>
       </c>
       <c r="G15" t="n">
-        <v>0.3602333333333333</v>
+        <v>1.451033333333333</v>
       </c>
       <c r="H15" t="n">
-        <v>0.3566666666666667</v>
+        <v>1.436666666666667</v>
       </c>
       <c r="I15" t="n">
         <v>25.2</v>
@@ -889,10 +889,10 @@
         <v>3.96</v>
       </c>
       <c r="G16" t="n">
-        <v>0.4803111111111111</v>
+        <v>1.571111111111111</v>
       </c>
       <c r="H16" t="n">
-        <v>0.4755555555555556</v>
+        <v>1.555555555555556</v>
       </c>
       <c r="I16" t="n">
         <v>25.2</v>
@@ -918,10 +918,10 @@
         <v>3.9</v>
       </c>
       <c r="G17" t="n">
-        <v>0.6003888888888889</v>
+        <v>1.691188888888889</v>
       </c>
       <c r="H17" t="n">
-        <v>0.5944444444444444</v>
+        <v>1.674444444444445</v>
       </c>
       <c r="I17" t="n">
         <v>25.2</v>
@@ -947,10 +947,10 @@
         <v>3.84</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7204666666666667</v>
+        <v>1.811266666666667</v>
       </c>
       <c r="H18" t="n">
-        <v>0.7133333333333334</v>
+        <v>1.793333333333333</v>
       </c>
       <c r="I18" t="n">
         <v>25.2</v>
@@ -976,10 +976,10 @@
         <v>3.78</v>
       </c>
       <c r="G19" t="n">
-        <v>0.8405444444444444</v>
+        <v>1.931344444444445</v>
       </c>
       <c r="H19" t="n">
-        <v>0.8322222222222222</v>
+        <v>1.912222222222222</v>
       </c>
       <c r="I19" t="n">
         <v>25.2</v>
@@ -1005,10 +1005,10 @@
         <v>3.72</v>
       </c>
       <c r="G20" t="n">
-        <v>0.9606222222222223</v>
+        <v>2.051422222222222</v>
       </c>
       <c r="H20" t="n">
-        <v>0.9511111111111111</v>
+        <v>2.031111111111111</v>
       </c>
       <c r="I20" t="n">
         <v>25.2</v>
@@ -1034,10 +1034,10 @@
         <v>3.66</v>
       </c>
       <c r="G21" t="n">
-        <v>1.0807</v>
+        <v>2.1715</v>
       </c>
       <c r="H21" t="n">
-        <v>1.07</v>
+        <v>2.15</v>
       </c>
       <c r="I21" t="n">
         <v>25.2</v>
